--- a/Team-Data/2013-14/1-25-2013-14.xlsx
+++ b/Team-Data/2013-14/1-25-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,55 +728,55 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F2" t="n">
         <v>20</v>
       </c>
       <c r="G2" t="n">
-        <v>0.535</v>
+        <v>0.524</v>
       </c>
       <c r="H2" t="n">
         <v>48.6</v>
       </c>
       <c r="I2" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="J2" t="n">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="L2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M2" t="n">
         <v>25.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0.367</v>
+        <v>0.364</v>
       </c>
       <c r="O2" t="n">
         <v>16.9</v>
       </c>
       <c r="P2" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="Q2" t="n">
         <v>0.781</v>
       </c>
       <c r="R2" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="S2" t="n">
         <v>31.7</v>
       </c>
       <c r="T2" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="U2" t="n">
         <v>25.4</v>
@@ -730,16 +797,16 @@
         <v>18.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>102.1</v>
+        <v>101.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
@@ -763,28 +830,28 @@
         <v>8</v>
       </c>
       <c r="AL2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM2" t="n">
         <v>4</v>
       </c>
-      <c r="AM2" t="n">
-        <v>3</v>
-      </c>
       <c r="AN2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO2" t="n">
         <v>18</v>
       </c>
       <c r="AP2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ2" t="n">
         <v>6</v>
       </c>
       <c r="AR2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AS2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT2" t="n">
         <v>26</v>
@@ -793,13 +860,13 @@
         <v>1</v>
       </c>
       <c r="AV2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX2" t="n">
         <v>20</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>21</v>
       </c>
       <c r="AY2" t="n">
         <v>12</v>
@@ -808,10 +875,10 @@
         <v>4</v>
       </c>
       <c r="BA2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC2" t="n">
         <v>13</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -921,16 +988,16 @@
         <v>-3.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>25</v>
       </c>
       <c r="AF3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH3" t="n">
         <v>28</v>
@@ -957,13 +1024,13 @@
         <v>23</v>
       </c>
       <c r="AP3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ3" t="n">
         <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS3" t="n">
         <v>21</v>
@@ -978,10 +1045,10 @@
         <v>24</v>
       </c>
       <c r="AW3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY3" t="n">
         <v>11</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -1103,13 +1170,13 @@
         <v>-2.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE4" t="n">
         <v>18</v>
       </c>
       <c r="AF4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AG4" t="n">
         <v>18</v>
@@ -1139,7 +1206,7 @@
         <v>6</v>
       </c>
       <c r="AP4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ4" t="n">
         <v>13</v>
@@ -1148,7 +1215,7 @@
         <v>25</v>
       </c>
       <c r="AS4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT4" t="n">
         <v>28</v>
@@ -1160,7 +1227,7 @@
         <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX4" t="n">
         <v>28</v>
@@ -1172,7 +1239,7 @@
         <v>24</v>
       </c>
       <c r="BA4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB4" t="n">
         <v>21</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E5" t="n">
         <v>19</v>
       </c>
       <c r="F5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>0.413</v>
+        <v>0.422</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
@@ -1225,49 +1292,49 @@
         <v>35.1</v>
       </c>
       <c r="J5" t="n">
-        <v>81.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.432</v>
+        <v>0.433</v>
       </c>
       <c r="L5" t="n">
         <v>5.6</v>
       </c>
       <c r="M5" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0.349</v>
+        <v>0.35</v>
       </c>
       <c r="O5" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="P5" t="n">
-        <v>24.7</v>
+        <v>25.1</v>
       </c>
       <c r="Q5" t="n">
         <v>0.73</v>
       </c>
       <c r="R5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="S5" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T5" t="n">
         <v>41.6</v>
       </c>
       <c r="U5" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V5" t="n">
         <v>12.8</v>
       </c>
       <c r="W5" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="X5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
         <v>5.7</v>
@@ -1276,13 +1343,13 @@
         <v>18.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>93.90000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3.2</v>
+        <v>-3.3</v>
       </c>
       <c r="AD5" t="n">
         <v>1</v>
@@ -1291,7 +1358,7 @@
         <v>18</v>
       </c>
       <c r="AF5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG5" t="n">
         <v>19</v>
@@ -1303,7 +1370,7 @@
         <v>28</v>
       </c>
       <c r="AJ5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK5" t="n">
         <v>27</v>
@@ -1315,19 +1382,19 @@
         <v>28</v>
       </c>
       <c r="AN5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AS5" t="n">
         <v>14</v>
@@ -1336,7 +1403,7 @@
         <v>23</v>
       </c>
       <c r="AU5" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AV5" t="n">
         <v>2</v>
@@ -1354,7 +1421,7 @@
         <v>3</v>
       </c>
       <c r="BA5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BB5" t="n">
         <v>28</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -1389,55 +1456,55 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F6" t="n">
         <v>21</v>
       </c>
       <c r="G6" t="n">
-        <v>0.512</v>
+        <v>0.5</v>
       </c>
       <c r="H6" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="I6" t="n">
         <v>34.6</v>
       </c>
       <c r="J6" t="n">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.426</v>
+        <v>0.427</v>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M6" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.342</v>
+        <v>0.338</v>
       </c>
       <c r="O6" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P6" t="n">
         <v>23.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.769</v>
+        <v>0.77</v>
       </c>
       <c r="R6" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="S6" t="n">
-        <v>33.1</v>
+        <v>33</v>
       </c>
       <c r="T6" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
       <c r="U6" t="n">
         <v>22.4</v>
@@ -1446,7 +1513,7 @@
         <v>15.8</v>
       </c>
       <c r="W6" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X6" t="n">
         <v>5.2</v>
@@ -1455,28 +1522,28 @@
         <v>6.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>92.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
       </c>
       <c r="AD6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE6" t="n">
         <v>13</v>
       </c>
-      <c r="AE6" t="n">
-        <v>12</v>
-      </c>
       <c r="AF6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH6" t="n">
         <v>1</v>
@@ -1485,13 +1552,13 @@
         <v>30</v>
       </c>
       <c r="AJ6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK6" t="n">
         <v>28</v>
       </c>
       <c r="AL6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM6" t="n">
         <v>27</v>
@@ -1506,13 +1573,13 @@
         <v>13</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT6" t="n">
         <v>6</v>
@@ -1521,10 +1588,10 @@
         <v>12</v>
       </c>
       <c r="AV6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AX6" t="n">
         <v>8</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -1649,19 +1716,19 @@
         <v>-5</v>
       </c>
       <c r="AD7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE7" t="n">
         <v>22</v>
       </c>
       <c r="AF7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG7" t="n">
         <v>22</v>
       </c>
       <c r="AH7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI7" t="n">
         <v>22</v>
@@ -1679,7 +1746,7 @@
         <v>23</v>
       </c>
       <c r="AN7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO7" t="n">
         <v>20</v>
@@ -1718,7 +1785,7 @@
         <v>8</v>
       </c>
       <c r="BA7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB7" t="n">
         <v>23</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>1.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1849,7 +1916,7 @@
         <v>3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK8" t="n">
         <v>4</v>
@@ -1858,13 +1925,13 @@
         <v>8</v>
       </c>
       <c r="AM8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AN8" t="n">
         <v>6</v>
       </c>
       <c r="AO8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP8" t="n">
         <v>27</v>
@@ -1885,7 +1952,7 @@
         <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F9" t="n">
         <v>21</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5</v>
+        <v>0.488</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
@@ -1956,37 +2023,37 @@
         <v>84.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0.363</v>
+        <v>0.362</v>
       </c>
       <c r="O9" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P9" t="n">
-        <v>25.9</v>
+        <v>25.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.727</v>
+        <v>0.732</v>
       </c>
       <c r="R9" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S9" t="n">
-        <v>33.5</v>
+        <v>33.3</v>
       </c>
       <c r="T9" t="n">
         <v>45.7</v>
       </c>
       <c r="U9" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V9" t="n">
         <v>15</v>
@@ -1998,37 +2065,37 @@
         <v>5.9</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>103.5</v>
+        <v>103.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AE9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AF9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AH9" t="n">
         <v>30</v>
       </c>
       <c r="AI9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ9" t="n">
         <v>6</v>
@@ -2037,28 +2104,28 @@
         <v>14</v>
       </c>
       <c r="AL9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AM9" t="n">
         <v>9</v>
       </c>
       <c r="AN9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AR9" t="n">
         <v>6</v>
       </c>
       <c r="AS9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AT9" t="n">
         <v>5</v>
@@ -2070,19 +2137,19 @@
         <v>13</v>
       </c>
       <c r="AW9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AZ9" t="n">
         <v>29</v>
       </c>
       <c r="BA9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB9" t="n">
         <v>11</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE10" t="n">
         <v>20</v>
@@ -2210,7 +2277,7 @@
         <v>16</v>
       </c>
       <c r="AI10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ10" t="n">
         <v>5</v>
@@ -2231,7 +2298,7 @@
         <v>17</v>
       </c>
       <c r="AP10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ10" t="n">
         <v>30</v>
@@ -2249,16 +2316,16 @@
         <v>23</v>
       </c>
       <c r="AV10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX10" t="n">
         <v>9</v>
       </c>
       <c r="AY10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ10" t="n">
         <v>15</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>4.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2389,7 +2456,7 @@
         <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI11" t="n">
         <v>4</v>
@@ -2419,7 +2486,7 @@
         <v>24</v>
       </c>
       <c r="AR11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS11" t="n">
         <v>3</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -2481,64 +2548,64 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E12" t="n">
         <v>29</v>
       </c>
       <c r="F12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>0.63</v>
+        <v>0.644</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="J12" t="n">
         <v>79.2</v>
       </c>
       <c r="K12" t="n">
-        <v>0.47</v>
+        <v>0.472</v>
       </c>
       <c r="L12" t="n">
         <v>9.1</v>
       </c>
       <c r="M12" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0.344</v>
+        <v>0.346</v>
       </c>
       <c r="O12" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="P12" t="n">
-        <v>31.1</v>
+        <v>31.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="R12" t="n">
         <v>11</v>
       </c>
       <c r="S12" t="n">
-        <v>33.9</v>
+        <v>34.1</v>
       </c>
       <c r="T12" t="n">
-        <v>44.9</v>
+        <v>45.1</v>
       </c>
       <c r="U12" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="V12" t="n">
         <v>16.1</v>
       </c>
       <c r="W12" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X12" t="n">
         <v>6</v>
@@ -2547,16 +2614,16 @@
         <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>105</v>
+        <v>105.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD12" t="n">
         <v>1</v>
@@ -2580,7 +2647,7 @@
         <v>28</v>
       </c>
       <c r="AK12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AL12" t="n">
         <v>6</v>
@@ -2604,34 +2671,34 @@
         <v>18</v>
       </c>
       <c r="AS12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AU12" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AV12" t="n">
         <v>28</v>
       </c>
       <c r="AW12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AX12" t="n">
         <v>3</v>
       </c>
       <c r="AY12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
       </c>
       <c r="BB12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC12" t="n">
         <v>9</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E13" t="n">
         <v>34</v>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>0.791</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H13" t="n">
         <v>48.2</v>
@@ -2681,37 +2748,37 @@
         <v>36.7</v>
       </c>
       <c r="J13" t="n">
-        <v>80.40000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="K13" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L13" t="n">
         <v>7.2</v>
       </c>
       <c r="M13" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0.364</v>
+        <v>0.363</v>
       </c>
       <c r="O13" t="n">
         <v>18.1</v>
       </c>
       <c r="P13" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.783</v>
+        <v>0.788</v>
       </c>
       <c r="R13" t="n">
         <v>10</v>
       </c>
       <c r="S13" t="n">
-        <v>35</v>
+        <v>34.8</v>
       </c>
       <c r="T13" t="n">
-        <v>45</v>
+        <v>44.8</v>
       </c>
       <c r="U13" t="n">
         <v>20.7</v>
@@ -2720,31 +2787,31 @@
         <v>15.5</v>
       </c>
       <c r="W13" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X13" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Y13" t="n">
         <v>4.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA13" t="n">
         <v>21.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>98.59999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AD13" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF13" t="n">
         <v>1</v>
@@ -2753,7 +2820,7 @@
         <v>1</v>
       </c>
       <c r="AH13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI13" t="n">
         <v>20</v>
@@ -2762,7 +2829,7 @@
         <v>27</v>
       </c>
       <c r="AK13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL13" t="n">
         <v>18</v>
@@ -2771,10 +2838,10 @@
         <v>22</v>
       </c>
       <c r="AN13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP13" t="n">
         <v>16</v>
@@ -2789,25 +2856,25 @@
         <v>2</v>
       </c>
       <c r="AT13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU13" t="n">
         <v>19</v>
       </c>
       <c r="AV13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW13" t="n">
         <v>20</v>
       </c>
       <c r="AX13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY13" t="n">
         <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA13" t="n">
         <v>6</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -2845,61 +2912,61 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E14" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F14" t="n">
         <v>15</v>
       </c>
       <c r="G14" t="n">
-        <v>0.674</v>
+        <v>0.667</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>38.4</v>
+        <v>38.2</v>
       </c>
       <c r="J14" t="n">
         <v>82.2</v>
       </c>
       <c r="K14" t="n">
-        <v>0.467</v>
+        <v>0.465</v>
       </c>
       <c r="L14" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.344</v>
+        <v>0.34</v>
       </c>
       <c r="O14" t="n">
         <v>20.9</v>
       </c>
       <c r="P14" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.731</v>
+        <v>0.728</v>
       </c>
       <c r="R14" t="n">
         <v>10.3</v>
       </c>
       <c r="S14" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="T14" t="n">
-        <v>42.8</v>
+        <v>43</v>
       </c>
       <c r="U14" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="V14" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="W14" t="n">
         <v>8.300000000000001</v>
@@ -2914,19 +2981,19 @@
         <v>21.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>106</v>
+        <v>105.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF14" t="n">
         <v>6</v>
@@ -2941,19 +3008,19 @@
         <v>11</v>
       </c>
       <c r="AJ14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK14" t="n">
         <v>6</v>
       </c>
       <c r="AL14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO14" t="n">
         <v>3</v>
@@ -2962,34 +3029,34 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AR14" t="n">
         <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU14" t="n">
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AW14" t="n">
         <v>10</v>
       </c>
       <c r="AX14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AY14" t="n">
         <v>2</v>
       </c>
       <c r="AZ14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA14" t="n">
         <v>2</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-5.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
         <v>22</v>
@@ -3129,7 +3196,7 @@
         <v>21</v>
       </c>
       <c r="AL15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM15" t="n">
         <v>5</v>
@@ -3144,13 +3211,13 @@
         <v>14</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR15" t="n">
         <v>23</v>
       </c>
       <c r="AS15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT15" t="n">
         <v>20</v>
@@ -3159,13 +3226,13 @@
         <v>10</v>
       </c>
       <c r="AV15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW15" t="n">
         <v>28</v>
       </c>
       <c r="AX15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY15" t="n">
         <v>13</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -3209,55 +3276,55 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F16" t="n">
         <v>20</v>
       </c>
       <c r="G16" t="n">
-        <v>0.524</v>
+        <v>0.512</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J16" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="K16" t="n">
-        <v>0.453</v>
+        <v>0.452</v>
       </c>
       <c r="L16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0.351</v>
+        <v>0.35</v>
       </c>
       <c r="O16" t="n">
-        <v>15.7</v>
+        <v>15.9</v>
       </c>
       <c r="P16" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.75</v>
+        <v>0.751</v>
       </c>
       <c r="R16" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S16" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="T16" t="n">
-        <v>43.3</v>
+        <v>43.1</v>
       </c>
       <c r="U16" t="n">
         <v>21.5</v>
@@ -3275,28 +3342,28 @@
         <v>5.6</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AB16" t="n">
         <v>95.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.2</v>
+        <v>-0.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AE16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF16" t="n">
         <v>10</v>
       </c>
       <c r="AG16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH16" t="n">
         <v>15</v>
@@ -3305,7 +3372,7 @@
         <v>17</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK16" t="n">
         <v>13</v>
@@ -3317,25 +3384,25 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO16" t="n">
         <v>27</v>
       </c>
       <c r="AP16" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AQ16" t="n">
         <v>20</v>
       </c>
       <c r="AR16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS16" t="n">
         <v>22</v>
       </c>
       <c r="AT16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AU16" t="n">
         <v>15</v>
@@ -3344,13 +3411,13 @@
         <v>3</v>
       </c>
       <c r="AW16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AY16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ16" t="n">
         <v>7</v>
@@ -3362,7 +3429,7 @@
         <v>25</v>
       </c>
       <c r="BC16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>5.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
@@ -3481,10 +3548,10 @@
         <v>5</v>
       </c>
       <c r="AH17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3496,7 +3563,7 @@
         <v>13</v>
       </c>
       <c r="AM17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN17" t="n">
         <v>7</v>
@@ -3508,7 +3575,7 @@
         <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3526,10 +3593,10 @@
         <v>17</v>
       </c>
       <c r="AW17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -3573,28 +3640,28 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E18" t="n">
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G18" t="n">
-        <v>0.186</v>
+        <v>0.19</v>
       </c>
       <c r="H18" t="n">
         <v>48.8</v>
       </c>
       <c r="I18" t="n">
-        <v>34.8</v>
+        <v>34.7</v>
       </c>
       <c r="J18" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.422</v>
+        <v>0.421</v>
       </c>
       <c r="L18" t="n">
         <v>7.2</v>
@@ -3603,31 +3670,31 @@
         <v>20.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0.343</v>
+        <v>0.345</v>
       </c>
       <c r="O18" t="n">
-        <v>14.5</v>
+        <v>14.7</v>
       </c>
       <c r="P18" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.751</v>
+        <v>0.756</v>
       </c>
       <c r="R18" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S18" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="T18" t="n">
         <v>41.2</v>
       </c>
       <c r="U18" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V18" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="W18" t="n">
         <v>7.1</v>
@@ -3639,19 +3706,19 @@
         <v>5.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AA18" t="n">
         <v>19.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>91.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>-9.4</v>
+        <v>-9</v>
       </c>
       <c r="AD18" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3681,7 +3748,7 @@
         <v>17</v>
       </c>
       <c r="AN18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO18" t="n">
         <v>30</v>
@@ -3690,10 +3757,10 @@
         <v>29</v>
       </c>
       <c r="AQ18" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AR18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS18" t="n">
         <v>28</v>
@@ -3705,22 +3772,22 @@
         <v>18</v>
       </c>
       <c r="AV18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW18" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AX18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY18" t="n">
         <v>19</v>
       </c>
       <c r="AZ18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB18" t="n">
         <v>30</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E19" t="n">
         <v>21</v>
       </c>
       <c r="F19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G19" t="n">
-        <v>0.488</v>
+        <v>0.5</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
@@ -3776,76 +3843,76 @@
         <v>89.09999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.436</v>
+        <v>0.437</v>
       </c>
       <c r="L19" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="M19" t="n">
         <v>22.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0.35</v>
+        <v>0.348</v>
       </c>
       <c r="O19" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="P19" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.783</v>
+        <v>0.782</v>
       </c>
       <c r="R19" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="S19" t="n">
         <v>32.6</v>
       </c>
       <c r="T19" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
       <c r="U19" t="n">
         <v>23.7</v>
       </c>
       <c r="V19" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W19" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Y19" t="n">
         <v>5.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="AA19" t="n">
         <v>22.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>106.8</v>
+        <v>106.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AD19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE19" t="n">
         <v>13</v>
       </c>
-      <c r="AE19" t="n">
-        <v>15</v>
-      </c>
       <c r="AF19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI19" t="n">
         <v>8</v>
@@ -3854,7 +3921,7 @@
         <v>1</v>
       </c>
       <c r="AK19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL19" t="n">
         <v>15</v>
@@ -3863,7 +3930,7 @@
         <v>12</v>
       </c>
       <c r="AN19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO19" t="n">
         <v>2</v>
@@ -3878,7 +3945,7 @@
         <v>2</v>
       </c>
       <c r="AS19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT19" t="n">
         <v>3</v>
@@ -3887,7 +3954,7 @@
         <v>5</v>
       </c>
       <c r="AV19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW19" t="n">
         <v>2</v>
@@ -3899,7 +3966,7 @@
         <v>24</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA19" t="n">
         <v>3</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AE20" t="n">
         <v>20</v>
@@ -4054,7 +4121,7 @@
         <v>15</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR20" t="n">
         <v>4</v>
@@ -4069,7 +4136,7 @@
         <v>14</v>
       </c>
       <c r="AV20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW20" t="n">
         <v>9</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -4197,13 +4264,13 @@
         <v>-3.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE21" t="n">
         <v>22</v>
       </c>
       <c r="AF21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG21" t="n">
         <v>22</v>
@@ -4215,7 +4282,7 @@
         <v>24</v>
       </c>
       <c r="AJ21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK21" t="n">
         <v>26</v>
@@ -4224,7 +4291,7 @@
         <v>7</v>
       </c>
       <c r="AM21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN21" t="n">
         <v>16</v>
@@ -4248,7 +4315,7 @@
         <v>27</v>
       </c>
       <c r="AU21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
@@ -4266,7 +4333,7 @@
         <v>28</v>
       </c>
       <c r="BA21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB21" t="n">
         <v>24</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E22" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F22" t="n">
         <v>10</v>
       </c>
       <c r="G22" t="n">
-        <v>0.778</v>
+        <v>0.773</v>
       </c>
       <c r="H22" t="n">
         <v>48.2</v>
@@ -4319,28 +4386,28 @@
         <v>39</v>
       </c>
       <c r="J22" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.471</v>
+        <v>0.47</v>
       </c>
       <c r="L22" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="M22" t="n">
         <v>20.1</v>
       </c>
       <c r="N22" t="n">
-        <v>0.35</v>
+        <v>0.353</v>
       </c>
       <c r="O22" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="P22" t="n">
         <v>25.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.806</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="R22" t="n">
         <v>11.3</v>
@@ -4349,37 +4416,37 @@
         <v>35.2</v>
       </c>
       <c r="T22" t="n">
-        <v>46.4</v>
+        <v>46.5</v>
       </c>
       <c r="U22" t="n">
         <v>21.4</v>
       </c>
       <c r="V22" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="W22" t="n">
         <v>8.1</v>
       </c>
       <c r="X22" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Y22" t="n">
         <v>3.9</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA22" t="n">
         <v>20.6</v>
       </c>
       <c r="AB22" t="n">
-        <v>105.3</v>
+        <v>105.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4394,22 +4461,22 @@
         <v>25</v>
       </c>
       <c r="AI22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ22" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AK22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AL22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM22" t="n">
         <v>20</v>
       </c>
       <c r="AN22" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO22" t="n">
         <v>4</v>
@@ -4427,7 +4494,7 @@
         <v>1</v>
       </c>
       <c r="AT22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU22" t="n">
         <v>16</v>
@@ -4448,10 +4515,10 @@
         <v>23</v>
       </c>
       <c r="BA22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC22" t="n">
         <v>3</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-5.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4573,13 +4640,13 @@
         <v>29</v>
       </c>
       <c r="AH23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI23" t="n">
         <v>21</v>
       </c>
       <c r="AJ23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK23" t="n">
         <v>19</v>
@@ -4600,13 +4667,13 @@
         <v>21</v>
       </c>
       <c r="AQ23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR23" t="n">
         <v>26</v>
       </c>
       <c r="AS23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT23" t="n">
         <v>21</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -4665,64 +4732,64 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E24" t="n">
         <v>14</v>
       </c>
       <c r="F24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G24" t="n">
-        <v>0.318</v>
+        <v>0.326</v>
       </c>
       <c r="H24" t="n">
         <v>48.8</v>
       </c>
       <c r="I24" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="J24" t="n">
-        <v>88.59999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="K24" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L24" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M24" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="N24" t="n">
-        <v>0.315</v>
+        <v>0.32</v>
       </c>
       <c r="O24" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="P24" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.708</v>
+        <v>0.709</v>
       </c>
       <c r="R24" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S24" t="n">
-        <v>33.1</v>
+        <v>33.3</v>
       </c>
       <c r="T24" t="n">
         <v>45</v>
       </c>
       <c r="U24" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="V24" t="n">
         <v>17.2</v>
       </c>
       <c r="W24" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="X24" t="n">
         <v>4.3</v>
@@ -4737,46 +4804,46 @@
         <v>20.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>101</v>
+        <v>101.3</v>
       </c>
       <c r="AC24" t="n">
-        <v>-8.5</v>
+        <v>-8.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG24" t="n">
         <v>27</v>
       </c>
-      <c r="AG24" t="n">
-        <v>28</v>
-      </c>
       <c r="AH24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK24" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL24" t="n">
         <v>23</v>
       </c>
       <c r="AM24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN24" t="n">
         <v>29</v>
       </c>
       <c r="AO24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP24" t="n">
         <v>17</v>
@@ -4785,13 +4852,13 @@
         <v>28</v>
       </c>
       <c r="AR24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU24" t="n">
         <v>11</v>
@@ -4812,7 +4879,7 @@
         <v>19</v>
       </c>
       <c r="BA24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB24" t="n">
         <v>14</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>3</v>
       </c>
       <c r="AD25" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AE25" t="n">
         <v>10</v>
@@ -4943,7 +5010,7 @@
         <v>9</v>
       </c>
       <c r="AJ25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK25" t="n">
         <v>11</v>
@@ -4955,7 +5022,7 @@
         <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO25" t="n">
         <v>15</v>
@@ -4979,19 +5046,19 @@
         <v>30</v>
       </c>
       <c r="AV25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW25" t="n">
         <v>7</v>
       </c>
       <c r="AX25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY25" t="n">
         <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA25" t="n">
         <v>13</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -5029,37 +5096,37 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E26" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F26" t="n">
         <v>11</v>
       </c>
       <c r="G26" t="n">
-        <v>0.75</v>
+        <v>0.744</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>40.6</v>
+        <v>40.4</v>
       </c>
       <c r="J26" t="n">
-        <v>88.59999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="K26" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L26" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0.39</v>
+        <v>0.392</v>
       </c>
       <c r="O26" t="n">
         <v>18.5</v>
@@ -5068,13 +5135,13 @@
         <v>22.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.823</v>
+        <v>0.824</v>
       </c>
       <c r="R26" t="n">
         <v>13.1</v>
       </c>
       <c r="S26" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="T26" t="n">
         <v>46.5</v>
@@ -5086,31 +5153,31 @@
         <v>13.6</v>
       </c>
       <c r="W26" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="X26" t="n">
         <v>4.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AA26" t="n">
         <v>20.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>109.5</v>
+        <v>109.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF26" t="n">
         <v>4</v>
@@ -5119,22 +5186,22 @@
         <v>4</v>
       </c>
       <c r="AH26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI26" t="n">
         <v>2</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL26" t="n">
         <v>1</v>
       </c>
       <c r="AM26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN26" t="n">
         <v>2</v>
@@ -5152,10 +5219,10 @@
         <v>3</v>
       </c>
       <c r="AS26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU26" t="n">
         <v>3</v>
@@ -5167,7 +5234,7 @@
         <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY26" t="n">
         <v>4</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -5289,13 +5356,13 @@
         <v>-2.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
       </c>
       <c r="AF27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG27" t="n">
         <v>25</v>
@@ -5307,31 +5374,31 @@
         <v>16</v>
       </c>
       <c r="AJ27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK27" t="n">
         <v>17</v>
       </c>
       <c r="AL27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM27" t="n">
         <v>21</v>
       </c>
       <c r="AN27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO27" t="n">
         <v>5</v>
       </c>
       <c r="AP27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ27" t="n">
         <v>12</v>
       </c>
       <c r="AR27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS27" t="n">
         <v>16</v>
@@ -5343,7 +5410,7 @@
         <v>27</v>
       </c>
       <c r="AV27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW27" t="n">
         <v>15</v>
@@ -5361,7 +5428,7 @@
         <v>4</v>
       </c>
       <c r="BB27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC27" t="n">
         <v>19</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="AD28" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5516,10 +5583,10 @@
         <v>28</v>
       </c>
       <c r="AS28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU28" t="n">
         <v>2</v>
@@ -5537,7 +5604,7 @@
         <v>17</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA28" t="n">
         <v>27</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E29" t="n">
         <v>22</v>
       </c>
       <c r="F29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G29" t="n">
-        <v>0.512</v>
+        <v>0.524</v>
       </c>
       <c r="H29" t="n">
         <v>48.6</v>
@@ -5593,37 +5660,37 @@
         <v>36</v>
       </c>
       <c r="J29" t="n">
-        <v>82.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L29" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="M29" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0.364</v>
+        <v>0.36</v>
       </c>
       <c r="O29" t="n">
-        <v>19</v>
+        <v>18.7</v>
       </c>
       <c r="P29" t="n">
-        <v>24.7</v>
+        <v>24.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.77</v>
+        <v>0.768</v>
       </c>
       <c r="R29" t="n">
         <v>12</v>
       </c>
       <c r="S29" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T29" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="U29" t="n">
         <v>20.4</v>
@@ -5632,10 +5699,10 @@
         <v>14.4</v>
       </c>
       <c r="W29" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X29" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y29" t="n">
         <v>4.7</v>
@@ -5647,22 +5714,22 @@
         <v>22</v>
       </c>
       <c r="AB29" t="n">
-        <v>99.2</v>
+        <v>98.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AE29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF29" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AG29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH29" t="n">
         <v>8</v>
@@ -5671,28 +5738,28 @@
         <v>26</v>
       </c>
       <c r="AJ29" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AK29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AM29" t="n">
         <v>11</v>
       </c>
-      <c r="AM29" t="n">
-        <v>10</v>
-      </c>
       <c r="AN29" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AO29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP29" t="n">
         <v>10</v>
       </c>
       <c r="AQ29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AR29" t="n">
         <v>9</v>
@@ -5704,19 +5771,19 @@
         <v>13</v>
       </c>
       <c r="AU29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV29" t="n">
         <v>9</v>
       </c>
       <c r="AW29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX29" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AY29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ29" t="n">
         <v>27</v>
@@ -5725,7 +5792,7 @@
         <v>5</v>
       </c>
       <c r="BB29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC29" t="n">
         <v>11</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F30" t="n">
         <v>29</v>
       </c>
       <c r="G30" t="n">
-        <v>0.341</v>
+        <v>0.326</v>
       </c>
       <c r="H30" t="n">
         <v>48.2</v>
@@ -5784,67 +5851,67 @@
         <v>6.6</v>
       </c>
       <c r="M30" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0.357</v>
+        <v>0.355</v>
       </c>
       <c r="O30" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="P30" t="n">
         <v>21.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.758</v>
+        <v>0.756</v>
       </c>
       <c r="R30" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S30" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T30" t="n">
         <v>41.3</v>
       </c>
       <c r="U30" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V30" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W30" t="n">
         <v>7</v>
       </c>
       <c r="X30" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y30" t="n">
         <v>4.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>94.7</v>
+        <v>94.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>-6.5</v>
+        <v>-6.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE30" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AF30" t="n">
         <v>26</v>
       </c>
       <c r="AG30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH30" t="n">
         <v>24</v>
@@ -5856,7 +5923,7 @@
         <v>24</v>
       </c>
       <c r="AK30" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AL30" t="n">
         <v>24</v>
@@ -5871,37 +5938,37 @@
         <v>25</v>
       </c>
       <c r="AP30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR30" t="n">
         <v>19</v>
       </c>
       <c r="AS30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT30" t="n">
         <v>24</v>
       </c>
       <c r="AU30" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AV30" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW30" t="n">
         <v>26</v>
       </c>
       <c r="AX30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY30" t="n">
         <v>18</v>
       </c>
       <c r="AZ30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA30" t="n">
         <v>16</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
@@ -5939,31 +6006,31 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E31" t="n">
         <v>21</v>
       </c>
       <c r="F31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G31" t="n">
-        <v>0.488</v>
+        <v>0.5</v>
       </c>
       <c r="H31" t="n">
         <v>48.8</v>
       </c>
       <c r="I31" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J31" t="n">
-        <v>83.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="K31" t="n">
         <v>0.449</v>
       </c>
       <c r="L31" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M31" t="n">
         <v>20.4</v>
@@ -5975,58 +6042,58 @@
         <v>15.9</v>
       </c>
       <c r="P31" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.733</v>
+        <v>0.73</v>
       </c>
       <c r="R31" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S31" t="n">
         <v>31.7</v>
       </c>
       <c r="T31" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="U31" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="V31" t="n">
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="W31" t="n">
         <v>8.5</v>
       </c>
       <c r="X31" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y31" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="AB31" t="n">
         <v>98.90000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="AD31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE31" t="n">
         <v>13</v>
       </c>
-      <c r="AE31" t="n">
-        <v>15</v>
-      </c>
       <c r="AF31" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG31" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH31" t="n">
         <v>3</v>
@@ -6035,7 +6102,7 @@
         <v>15</v>
       </c>
       <c r="AJ31" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AK31" t="n">
         <v>16</v>
@@ -6053,46 +6120,46 @@
         <v>26</v>
       </c>
       <c r="AP31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ31" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AR31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS31" t="n">
         <v>17</v>
       </c>
       <c r="AT31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU31" t="n">
         <v>9</v>
       </c>
       <c r="AV31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ31" t="n">
         <v>16</v>
       </c>
       <c r="BA31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-25-2013-14</t>
+          <t>2014-01-25</t>
         </is>
       </c>
     </row>
